--- a/tame_output/ON/bt/strategyON_20240213.xlsx
+++ b/tame_output/ON/bt/strategyON_20240213.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-02-11</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>17.7%</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-02-11</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-02-11</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-02-11</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-02-11</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.3%</t>
+          <t>-155.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-02-11</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.0%</t>
+          <t>120.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1871"/>
+  <dimension ref="A1:G1872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.420448635964887</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44594,6 +44594,29 @@
       </c>
       <c r="G1871" t="n">
         <v>4.467075582334768</v>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" s="2" t="n">
+        <v>45334</v>
+      </c>
+      <c r="B1872" t="n">
+        <v>3.458007309937238</v>
+      </c>
+      <c r="C1872" t="n">
+        <v>3.113033748966606</v>
+      </c>
+      <c r="D1872" t="n">
+        <v>1.617972900648867</v>
+      </c>
+      <c r="E1872" t="n">
+        <v>3.759866484912405</v>
+      </c>
+      <c r="F1872" t="n">
+        <v>2.25656622007763</v>
+      </c>
+      <c r="G1872" t="n">
+        <v>4.466973481013184</v>
       </c>
     </row>
   </sheetData>
